--- a/老虎机游戏开箱文索引.xlsx
+++ b/老虎机游戏开箱文索引.xlsx
@@ -1140,6 +1140,9 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:H44" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -2016,6 +2019,9 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L56" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -2364,6 +2370,9 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L34" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -2712,6 +2721,9 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L34" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -3012,5 +3024,8 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L32" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/老虎机游戏开箱文索引.xlsx
+++ b/老虎机游戏开箱文索引.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="4" name="第2页（No.011-022）" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="第3页（No.001-010）" state="visible" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -631,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -655,6 +655,24 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1004,130 +1022,130 @@
   </cols>
   <sheetData>
     <row r="1" ht="26.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="33" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
     </row>
     <row r="5" ht="33" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
     </row>
     <row r="6" ht="33" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
     </row>
     <row r="7" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17" ht="33" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="10" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="10" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1196,784 +1214,784 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="F8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="D10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="F10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="8" t="s">
+      <c r="F12" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="8" t="s">
+      <c r="F13" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="D14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="F14" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="D15" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="8" t="s">
+      <c r="F15" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="D16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="8" t="s">
+      <c r="F16" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="8" t="s">
+      <c r="F17" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="8" t="s">
+      <c r="F18" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="D19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="8" t="s">
+      <c r="F19" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="D20" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="F20" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="D21" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="8" t="s">
+      <c r="F21" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="8" t="s">
+      <c r="F22" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="D23" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="F23" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="8" t="s">
+      <c r="F23" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="D24" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="8" t="s">
+      <c r="F24" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="D25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="F25" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G25" s="8" t="s">
+      <c r="F25" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="D26" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="F26" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G26" s="8" t="s">
+      <c r="F26" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="6" t="s">
+      <c r="D27" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G27" s="8" t="s">
+      <c r="F27" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="6" t="s">
+      <c r="D28" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="F28" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="8" t="s">
+      <c r="F28" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="6" t="s">
+      <c r="D29" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G29" s="8" t="s">
+      <c r="F29" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="D30" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" s="6" t="s">
+      <c r="D31" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="D32" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="D33" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E33" s="6" t="s">
+      <c r="D33" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="34" ht="75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D34" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34" s="6" t="s">
+      <c r="D34" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="35" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="D35" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="36" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36" s="6" t="s">
+      <c r="D36" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="14" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2075,278 +2093,278 @@
       </c>
     </row>
     <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="5" ht="75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="D10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="F10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="8" t="s">
+      <c r="F12" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="8" t="s">
+      <c r="F13" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="D14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="F14" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2426,278 +2444,278 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="F8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="D10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="F10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="8" t="s">
+      <c r="F12" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="8" t="s">
+      <c r="F13" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="D14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="F14" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2777,232 +2795,232 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="F8" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="D10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="F10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="8" t="s">
+      <c r="F12" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>34</v>
       </c>
     </row>
